--- a/Дело3а-78-2026Таганай/11_Поставщики/19. Сибирское здоровье/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/19. Сибирское здоровье/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92540238101</v>
+        <v>46157.93114326482</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/19. Сибирское здоровье/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/19. Сибирское здоровье/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93114326482</v>
+        <v>46157.93368331043</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/19. Сибирское здоровье/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/19. Сибирское здоровье/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93368331043</v>
+        <v>46157.93672231751</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/19. Сибирское здоровье/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/19. Сибирское здоровье/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93672231751</v>
+        <v>46158.28194236741</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/19. Сибирское здоровье/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/19. Сибирское здоровье/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28194236741</v>
+        <v>46158.29718443078</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/19. Сибирское здоровье/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/19. Сибирское здоровье/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29718443078</v>
+        <v>46158.29790528245</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/19. Сибирское здоровье/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/19. Сибирское здоровье/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29790528245</v>
+        <v>46158.33355990575</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/19. Сибирское здоровье/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/19. Сибирское здоровье/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33355990575</v>
+        <v>46158.37210816445</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/19. Сибирское здоровье/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/19. Сибирское здоровье/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37210816445</v>
+        <v>46158.372678075</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
